--- a/data_input/monthly/2026-07.xlsx
+++ b/data_input/monthly/2026-07.xlsx
@@ -16,24 +16,25 @@
     <sheet name="fact_promo_day" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="fact_lto_line" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="fact_partner" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="booking" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ads_month" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="ads_brand" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ads_objective" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ads_campaign_detail" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="social_month" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="member" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="store_month" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="daily" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="coverage" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="dim_target" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="oa" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="ads_google" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="gads_channel" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="cogs_cov" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="voucher_month" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="voucher_join" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="social_post" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="daily_party" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="booking" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ads_month" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ads_brand" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ads_objective" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ads_campaign_detail" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="social_month" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="member" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="store_month" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="daily" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="coverage" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="dim_target" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="oa" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="ads_google" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="gads_channel" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="cogs_cov" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="voucher_month" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="voucher_join" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="social_post" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A91"/>
+  <dimension ref="A1:A93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -783,306 +784,320 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   booking                   42 dòng   bắt buộc: month, status</t>
+          <t xml:space="preserve">   daily_party               54 dòng   bắt buộc: date, store, net, tc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
+          <t xml:space="preserve">                                  Phần KHÁCH TIỆC của `daily`: chỉ các hoá đơn có Số khách ≥ $guest_segment.party_min_guests, gộp theo NGÀY × cửa hàng. ETL tự sinh từ bảng kê hoá đơn (S02). Khách lẻ = daily − daily_party.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_month                  1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   booking                   42 dòng   bắt buộc: month, status</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Meta Ads tổng theo tháng. CHỈ cộng dòng cấp campaign — cộng cả adset là nhân đôi.</t>
+          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_brand                  4 dòng   bắt buộc: month, brand</t>
+          <t xml:space="preserve">   ads_month                  1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Meta Ads theo brand. Nhãn `Tuyển dụng` không phải marketing thương hiệu.</t>
+          <t xml:space="preserve">                                  Meta Ads tổng theo tháng. CHỈ cộng dòng cấp campaign — cộng cả adset là nhân đôi.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_objective              5 dòng   bắt buộc: month, objective</t>
+          <t xml:space="preserve">   ads_brand                  4 dòng   bắt buộc: month, brand</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Meta Ads theo mục tiêu chiến dịch.</t>
+          <t xml:space="preserve">                                  Meta Ads theo brand. Nhãn `Tuyển dụng` không phải marketing thương hiệu.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_campaign_detail       20 dòng   bắt buộc: month, brand, objective, campaign</t>
+          <t xml:space="preserve">   ads_objective              5 dòng   bắt buộc: month, objective</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Chi tiết từng chiến dịch Meta trong tháng. page = mã fanpage đầu tên chiến dịch · rkind = loại kết quả chuẩn hoá · funnel = 'booking' nếu thuộc phễu booking tiệc (luật $booking.ads).</t>
+          <t xml:space="preserve">                                  Meta Ads theo mục tiêu chiến dịch.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: cpr</t>
+          <t xml:space="preserve">   ads_campaign_detail       20 dòng   bắt buộc: month, brand, objective, campaign</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   social_month               5 dòng   bắt buộc: month, platform, brand</t>
+          <t xml:space="preserve">                                  Chi tiết từng chiến dịch Meta trong tháng. page = mã fanpage đầu tên chiến dịch · rkind = loại kết quả chuẩn hoá · funnel = 'booking' nếu thuộc phễu booking tiệc (luật $booking.ads).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Fanpage &amp; TikTok. Facebook điền reach · TikTok điền views — KHÔNG gộp hai cột. platform ∈ FACEBOOK|TIKTOK|INSTAGRAM|YOUTUBE|ZALO code = mã fanpage (NCB · NDC · NJFB · NEC). contacts = Tổng số người liên hệ, msgs = Lượt bắt đầu cuộc trò chuyện qua tin nhắn (Facebook, cả tự nhiên lẫn trả phí).</t>
+          <t xml:space="preserve">                                  loader tự tính: cpr</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: net_follow, er, reach_rate, per_post, cpm, audience, unit</t>
+          <t xml:space="preserve">   social_month               5 dòng   bắt buộc: month, platform, brand</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   member                     1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">                                  Fanpage &amp; TikTok. Facebook điền reach · TikTok điền views — KHÔNG gộp hai cột. platform ∈ FACEBOOK|TIKTOK|INSTAGRAM|YOUTUBE|ZALO code = mã fanpage (NCB · NDC · NJFB · NEC). contacts = Tổng số người liên hệ, msgs = Lượt bắt đầu cuộc trò chuyện qua tin nhắn (Facebook, cả tự nhiên lẫn trả phí).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Member đăng ký mới &amp; OA follow mới theo tháng (số toàn chuỗi).</t>
+          <t xml:space="preserve">                                  loader tự tính: net_follow, er, reach_rate, per_post, cpm, audience, unit</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   store_month               10 dòng   bắt buộc: month, store, net, guest, tc</t>
+          <t xml:space="preserve">   member                     1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
+          <t xml:space="preserve">                                  Member đăng ký mới &amp; OA follow mới theo tháng (số toàn chuỗi).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
+          <t xml:space="preserve">   store_month               10 dòng   bắt buộc: month, store, net, guest, tc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daily                    268 dòng   bắt buộc: date, store, net</t>
+          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
+          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   daily                    268 dòng   bắt buộc: date, store, net</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
+          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: partial</t>
+          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   dim_target                 7 dòng   bắt buộc: month, store, target</t>
+          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Target doanh thu theo cửa hàng × tháng. Được phép khai cả tháng tương lai.</t>
+          <t xml:space="preserve">                                  loader tự tính: partial</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   oa                         1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   dim_target                 7 dòng   bắt buộc: month, store, target</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Zalo OA. follows = Quan tâm · views = Xem trang thông tin OA · menu = Tương tác thanh menu · content = Xem nội dung.</t>
+          <t xml:space="preserve">                                  Target doanh thu theo cửa hàng × tháng. Được phép khai cả tháng tương lai.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_google                 5 dòng   bắt buộc: month, campaign</t>
+          <t xml:space="preserve">   oa                         1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Google Ads theo chiến dịch. Đã loại dòng 'Tổng số: …'.</t>
+          <t xml:space="preserve">                                  Zalo OA. follows = Quan tâm · views = Xem trang thông tin OA · menu = Tương tác thanh menu · content = Xem nội dung.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: cpa</t>
+          <t xml:space="preserve">   ads_google                 5 dòng   bắt buộc: month, campaign</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   gads_channel               7 dòng   bắt buộc: month, channel</t>
+          <t xml:space="preserve">                                  Google Ads theo chiến dịch. Đã loại dòng 'Tổng số: …'.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Google Ads theo kênh phân phối (Maps, Tìm kiếm, YouTube…).</t>
+          <t xml:space="preserve">                                  loader tự tính: cpa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   cogs_cov                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   gads_channel               7 dòng   bắt buộc: month, channel</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Độ phủ giá vốn theo tháng.</t>
+          <t xml:space="preserve">                                  Google Ads theo kênh phân phối (Maps, Tìm kiếm, YouTube…).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: pct</t>
+          <t xml:space="preserve">   cogs_cov                   1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_month              4 dòng   bắt buộc: m, brand</t>
+          <t xml:space="preserve">                                  Độ phủ giá vốn theo tháng.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
+          <t xml:space="preserve">                                  loader tự tính: pct</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_join               1 dòng   bắt buộc: m</t>
+          <t xml:space="preserve">   voucher_month              4 dòng   bắt buộc: m, brand</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Tỷ lệ voucher khớp được với hoá đơn trong cùng tháng.</t>
+          <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: rate</t>
+          <t xml:space="preserve">   voucher_join               1 dòng   bắt buộc: m</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   social_post               22 dòng   bắt buộc: date, platform, brand, page, title</t>
+          <t xml:space="preserve">                                  Tỷ lệ voucher khớp được với hoá đơn trong cùng tháng.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Bài đăng / video. watch_avg tính bằng GIÂY.</t>
+          <t xml:space="preserve">                                  loader tự tính: rate</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   social_post               22 dòng   bắt buộc: date, platform, brand, page, title</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  Bài đăng / video. watch_avg tính bằng GIÂY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">                                  loader tự tính: engage, audience, er, unit</t>
         </is>
@@ -1094,6 +1109,1188 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2246300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>158000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4508784</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2173000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>257000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3701603</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6434867</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10871532</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>79000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6729156</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>14996184</v>
+      </c>
+      <c r="D12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>38771116</v>
+      </c>
+      <c r="D13" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>13085999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3320000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>21</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1387000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>14223006</v>
+      </c>
+      <c r="D17" t="n">
+        <v>22</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3705005</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12732476</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>6111000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2102000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6235828</v>
+      </c>
+      <c r="D22" t="n">
+        <v>14</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>375000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>198000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>22</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1366754</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10380657</v>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3278224</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>409500</v>
+      </c>
+      <c r="D28" t="n">
+        <v>14</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2249000</v>
+      </c>
+      <c r="D29" t="n">
+        <v>14</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4935168</v>
+      </c>
+      <c r="D30" t="n">
+        <v>14</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1110000</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>21</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>837600</v>
+      </c>
+      <c r="D33" t="n">
+        <v>23</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>48821262</v>
+      </c>
+      <c r="D34" t="n">
+        <v>111</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7775951</v>
+      </c>
+      <c r="D35" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>41871300</v>
+      </c>
+      <c r="D36" t="n">
+        <v>35</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>664000</v>
+      </c>
+      <c r="D37" t="n">
+        <v>23</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1408000</v>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>582876</v>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1078000</v>
+      </c>
+      <c r="D40" t="n">
+        <v>11</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3823735</v>
+      </c>
+      <c r="D41" t="n">
+        <v>13</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2104000</v>
+      </c>
+      <c r="D42" t="n">
+        <v>14</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>516000</v>
+      </c>
+      <c r="D43" t="n">
+        <v>11</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>42012571</v>
+      </c>
+      <c r="D44" t="n">
+        <v>63</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D45" t="n">
+        <v>19</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2494346</v>
+      </c>
+      <c r="D46" t="n">
+        <v>11</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>891324</v>
+      </c>
+      <c r="D47" t="n">
+        <v>11</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>855000</v>
+      </c>
+      <c r="D48" t="n">
+        <v>13</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>6864329</v>
+      </c>
+      <c r="D49" t="n">
+        <v>23</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5042600</v>
+      </c>
+      <c r="D50" t="n">
+        <v>33</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>237000</v>
+      </c>
+      <c r="D51" t="n">
+        <v>13</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5044433</v>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>121315800</v>
+      </c>
+      <c r="D53" t="n">
+        <v>230</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3301650</v>
+      </c>
+      <c r="D54" t="n">
+        <v>51</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>19309752</v>
+      </c>
+      <c r="D55" t="n">
+        <v>20</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4245,7 +5442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4312,7 +5509,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4426,7 +5623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4558,7 +5755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5598,7 +6795,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6001,7 +7198,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6059,7 +7256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6389,7 +7586,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12058,77 +13255,6 @@
       </c>
       <c r="E269" t="n">
         <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>days_data</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>days_month</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>first</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>last</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>31</v>
-      </c>
-      <c r="C2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -12295,6 +13421,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>days_data</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>days_month</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>first</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>last</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12430,7 +13627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12515,7 +13712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12798,7 +13995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13020,7 +14217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13081,131 +14278,6 @@
       </c>
       <c r="F2" t="n">
         <v>0.4073</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>used</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>rev</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>disc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>240</v>
-      </c>
-      <c r="D2" t="n">
-        <v>48177000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8719600</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8356000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1671200</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NJFB</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" t="n">
-        <v>29191500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5838300</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Không rõ</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>59000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>11800</v>
       </c>
     </row>
   </sheetData>
@@ -13219,7 +14291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13230,12 +14302,22 @@
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>brand</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>hit</t>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>disc</t>
         </is>
       </c>
     </row>
@@ -13245,11 +14327,82 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>269</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>268</v>
+        <v>240</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48177000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8719600</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8356000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1671200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>29191500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5838300</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Không rõ</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>59000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11800</v>
       </c>
     </row>
   </sheetData>
@@ -13258,6 +14411,50 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>269</v>
+      </c>
+      <c r="C2" t="n">
+        <v>268</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -97658,7 +98855,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PTTT</t>
+          <t>XAC_NHAN</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -97706,7 +98903,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PTTT</t>
+          <t>XAC_NHAN</t>
         </is>
       </c>
       <c r="G8" t="n">
